--- a/public/forms/OOO_MasterPlan.xlsx
+++ b/public/forms/OOO_MasterPlan.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20382"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melephant\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\민원4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0022055B-3460-4615-9906-95543F90093D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D5D66C-6CCC-40FD-B492-7B2CD4AF8135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
+    <workbookView xWindow="270" yWindow="150" windowWidth="20355" windowHeight="12465" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
   <si>
     <t>학생</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -151,6 +151,13 @@
   </si>
   <si>
     <t>==&gt; 필수항목 아님</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>순서</t>
+  </si>
+  <si>
+    <t>분</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -263,7 +270,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -279,7 +286,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -575,10 +582,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B3B65D-4A8A-4A38-BA06-796CDFD70E5F}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -588,13 +595,14 @@
       <c r="C1" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="D1" s="7"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -604,23 +612,24 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -630,8 +639,9 @@
       <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -641,20 +651,22 @@
       <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -662,52 +674,62 @@
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="5" t="s">
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5" t="s">
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>3</v>
       </c>
@@ -715,31 +737,31 @@
         <v>8</v>
       </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>1</v>
       </c>
-      <c r="D13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13">
+      <c r="E13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13">
         <v>8</v>
       </c>
-      <c r="F13">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13">
+      <c r="I13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13">
         <v>8</v>
       </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>2</v>
-      </c>
       <c r="K13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -748,31 +770,52 @@
         <v>2</v>
       </c>
       <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>2</v>
+      </c>
+      <c r="R13">
         <v>15</v>
       </c>
-      <c r="O13">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>1</v>
       </c>
-      <c r="P13" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q13">
+      <c r="U13" t="s">
+        <v>2</v>
+      </c>
+      <c r="V13">
         <v>8</v>
       </c>
-      <c r="R13">
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>1</v>
       </c>
-      <c r="S13" t="s">
-        <v>2</v>
-      </c>
-      <c r="T13">
+      <c r="Y13" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z13">
         <v>8</v>
       </c>
-      <c r="U13">
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -780,64 +823,85 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
         <v>4</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>12</v>
       </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
         <v>4</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>12</v>
       </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14" t="s">
         <v>4</v>
       </c>
-      <c r="K14">
+      <c r="N14">
         <v>12</v>
       </c>
-      <c r="L14">
-        <v>2</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="s">
         <v>6</v>
       </c>
-      <c r="N14">
+      <c r="R14">
         <v>18</v>
       </c>
-      <c r="O14">
-        <v>2</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="U14" t="s">
         <v>4</v>
       </c>
-      <c r="Q14">
+      <c r="V14">
         <v>12</v>
       </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14" t="s">
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="s">
         <v>4</v>
       </c>
-      <c r="T14">
+      <c r="Z14">
         <v>12</v>
       </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -845,31 +909,31 @@
         <v>13</v>
       </c>
       <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="D15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15">
+      <c r="E15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15">
         <v>13</v>
       </c>
-      <c r="F15">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>3</v>
       </c>
-      <c r="G15" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15">
+      <c r="I15" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15">
         <v>13</v>
       </c>
-      <c r="I15">
-        <v>3</v>
-      </c>
-      <c r="J15" t="s">
-        <v>2</v>
-      </c>
       <c r="K15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>3</v>
@@ -878,31 +942,52 @@
         <v>2</v>
       </c>
       <c r="N15">
+        <v>13</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>2</v>
+      </c>
+      <c r="R15">
         <v>19</v>
       </c>
-      <c r="O15">
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
         <v>3</v>
       </c>
-      <c r="P15" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q15">
+      <c r="U15" t="s">
+        <v>2</v>
+      </c>
+      <c r="V15">
         <v>13</v>
       </c>
-      <c r="R15">
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
         <v>3</v>
       </c>
-      <c r="S15" t="s">
-        <v>2</v>
-      </c>
-      <c r="T15">
+      <c r="Y15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z15">
         <v>13</v>
       </c>
-      <c r="U15">
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -910,64 +995,85 @@
         <v>18</v>
       </c>
       <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>15</v>
       </c>
-      <c r="F16">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>4</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>6</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>18</v>
       </c>
-      <c r="I16">
-        <v>4</v>
-      </c>
-      <c r="J16" t="s">
-        <v>6</v>
-      </c>
       <c r="K16">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>4</v>
       </c>
       <c r="M16" t="s">
+        <v>6</v>
+      </c>
+      <c r="N16">
+        <v>18</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="s">
         <v>8</v>
       </c>
-      <c r="N16">
+      <c r="R16">
         <v>23</v>
       </c>
-      <c r="O16">
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
         <v>4</v>
       </c>
-      <c r="P16" t="s">
+      <c r="U16" t="s">
         <v>6</v>
       </c>
-      <c r="Q16">
+      <c r="V16">
         <v>18</v>
       </c>
-      <c r="R16">
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
         <v>4</v>
       </c>
-      <c r="S16" t="s">
+      <c r="Y16" t="s">
         <v>6</v>
       </c>
-      <c r="T16">
+      <c r="Z16">
         <v>18</v>
       </c>
-      <c r="U16">
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -975,55 +1081,73 @@
         <v>19</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>5</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>17</v>
       </c>
-      <c r="F17">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>5</v>
       </c>
-      <c r="G17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H17">
+      <c r="I17" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17">
         <v>19</v>
       </c>
-      <c r="I17">
-        <v>5</v>
-      </c>
-      <c r="J17" t="s">
-        <v>2</v>
-      </c>
       <c r="K17">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>5</v>
       </c>
-      <c r="P17" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q17">
+      <c r="M17" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17">
         <v>19</v>
       </c>
-      <c r="R17">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
         <v>5</v>
       </c>
-      <c r="S17" t="s">
-        <v>2</v>
-      </c>
-      <c r="T17">
+      <c r="U17" t="s">
+        <v>2</v>
+      </c>
+      <c r="V17">
         <v>19</v>
       </c>
-      <c r="U17">
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="Y17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z17">
+        <v>19</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
@@ -1031,51 +1155,69 @@
         <v>1</v>
       </c>
       <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>6</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>9</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>6</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>8</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>23</v>
       </c>
-      <c r="I18">
-        <v>6</v>
-      </c>
-      <c r="J18" t="s">
-        <v>8</v>
-      </c>
       <c r="K18">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
-      <c r="P18" t="s">
+      <c r="M18" t="s">
         <v>8</v>
       </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
+      <c r="N18">
+        <v>23</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
         <v>6</v>
       </c>
-      <c r="S18" t="s">
+      <c r="U18" t="s">
         <v>8</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>6</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
         <v>6</v>
       </c>
     </row>
